--- a/dosyalar/excel-klinigi/ExcelKlinigi_ANTRENMAN_Gunlugu.xlsx
+++ b/dosyalar/excel-klinigi/ExcelKlinigi_ANTRENMAN_Gunlugu.xlsx
@@ -32,7 +32,7 @@
     <t xml:space="preserve">ANTRENMAN  |  Antrenman günlüğü</t>
   </si>
   <si>
-    <t xml:space="preserve">Hangi harekette ne kaldırdın, rekorun ne, haftalık ve aylık yükün nasıl gidiyor.</t>
+    <t xml:space="preserve">Hangi harekette ne kaldırdın, rekorun ne, aylık yükün nasıl gidiyor.</t>
   </si>
   <si>
     <t xml:space="preserve">NASIL KULLANILIR</t>
